--- a/data/trans_bre/IQ09_D_R3-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IQ09_D_R3-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -522,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que llevan más tiempo (cuartil más desfavorable) sufriendo esa dolencia, enfermedad o impedimento que le haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Menores que llevan más tiempo (cuartil más desfavorable: más de 2161 días) sufriendo esa dolencia, enfermedad o impedimento que le haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -610,299 +619,137 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-15,35</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,45</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>25,55%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-15.3508632937801</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>7.448558261094224</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.2554820671733918</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-60,62; 57,43</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>-60.61559515665527</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>57.43087441927516</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-15,69</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-60,07</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-67,08; 0,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 0,0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-15.69387000873019</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-60.06975548430852</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-48,76</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-24,04</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="n">
+        <v>-67.07998840488295</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 0,0</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +757,151 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-16,55</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-3,0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-12,41</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-20,83%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-48.76260014746524</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-24.03753213823167</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-67,77; 0,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-21,11; 19,06</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-40,37; 0,0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 752,75</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>64,06</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,23</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11,89</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10,99</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>34,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-21,35; 30,88</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 49,46</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-39,85; 68,6</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-16.54616388214221</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-2.998050636605587</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-12.4130360683126</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2082806906791977</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-49,01</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-41,05</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>46,49</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>296,5%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-67.76521537247326</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-21.11134057745644</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="n">
+        <v>-40.37296388476735</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 0,0</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-81,01; 0,0</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-29,7; 88,54</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>19.06369224419645</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="n">
+        <v>7.527461664753078</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +909,259 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-6,64</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-7,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,77</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,77</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-35,72%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-47,17%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-49,37%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-2,86%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>64.06167149829507</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.2301506033781195</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>11.89472971601308</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>10.98944120152509</v>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.02311019808081636</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.34752232227085</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-24,93; 18,23</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-19,66; 7,11</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-16,18; 10,87</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-23,3; 23,69</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 427,63</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 121,19</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-68,81; 167,41</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-21.34814935687164</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-39.84533381480356</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>30.88147043833246</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>49.45783321037182</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>68.59712128493078</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-49.00875750161596</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-41.05060348149971</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>46.49247393549648</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="6" t="n">
+        <v>2.964983444627817</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-81.00609652859544</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="n">
+        <v>-29.70067181613921</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="n">
+        <v>88.5387294873517</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-6.64167653400964</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-6.999714636732748</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-4.773308317797691</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.7725926216289813</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.3571706624071247</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.4716718011005295</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.4937073754408879</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.02864613668084839</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-24.93352145876094</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-19.65904878706851</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-16.18362771826398</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-23.3010840411407</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="6" t="n">
+        <v>-0.6880822449567791</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>18.23122870530356</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>7.107449071170334</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>10.86617159885504</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>23.69179061301939</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>4.276312151126732</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1.211906737330072</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr"/>
+      <c r="J24" s="6" t="n">
+        <v>1.674091255392954</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1169,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
